--- a/justdial_leads.xlsx
+++ b/justdial_leads.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E137"/>
+  <dimension ref="A1:E197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4085,6 +4085,1626 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Shreya Medical Centre</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>http://www.shreyaclinics.in</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Shreya-Medical-Centre-Near-Sboa-School-Junior-College-Anna-Nagar-West-Extension/044P1235367473I2C7H2_BZDET</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>07411657051</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Homeocare International Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>http://www.homeocare.in</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Homeocare-International-Pvt-Ltd-Besides-Aarthi-Scans-Tambaram-West/044PXX44-XX44-140515163104-S5H1_BZDET</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>09731979204</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Sukra Hospital</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>http://www.sukrahospital.com</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Sukra-Hospital-Near-Karupatti-Coffe-Viduthalai-Nagar-S-Kolathur/044PXX44-XX44-170311011501-N2D9_BZDET</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>08904624213</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Medway Hospitals</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>http://www.medwayhospitals.com</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Medway-Hospitals-Mogappair-West/044PXX44-XX44-210716135004-G5B8_BZDET</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>08147455375</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Lotus Polycl</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>https://www.lotuspolyclinic.com</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Lotus-Polyclinic-Ponmar/044PXX44-XX44-251124222724-I1Y7_BZDET</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>08490993526</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Sanjeevi Pharma</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>http://www.sanjeevipharma.com</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Sanjeevi-Pharma-Opp-To-Anna-Siddha-Medical-College-Arumbakkam/044P7019021_BZDET</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>08147817803</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Priya Ortho Cl</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Priya-Ortho-Clinic-Near-Union-Bank-Tambaram-West/044PXX44-XX44-150723191046-T9C2_BZDET</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>08904959752</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Smile Garden Dental And Orthodontic Centre</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>http://www.smilegarden.in</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Smile-Garden-Dental-And-Orthodontic-Centre-Above-Kvb-Velacheri/044PXX44-XX44-090804235029-Z9V5_BZDET</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>08123969926</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>The Bio Cl</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/The-Bio-Clinical-Laboratory-Near-Chinmya-Nagar-Bridge-Behind-Gowri-Medicals-Virugambakkam/044P9808995_BZDET</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>08147934550</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Apollo Cl</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>http://www.apolloclinic.com/clinic-locator/india/tamil-nadu/chennai/porur</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Apollo-Clinic-Opp-Tanisq-Showroom-Opp-Prestige-Bella-Vista-Apts-Kattupakkam/044PXX44-XX44-230905160944-C6V5_BZDET</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>08460418794</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Supreme Speciality Hospitals</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>http://www.supremehospitals.in</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Supreme-Speciality-Hospitals-Near-Padur-Bus-Stop-Padur/044PXX44-XX44-180314121948-K5P3_BZDET</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>07022443343</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Prepco Healthcare OPC Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Prepco-Healthcare-OPC-Pvt-Ltd-Anna-Nagar/044PXX44-XX44-251006163946-R8W8_BZDET</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>09606283862</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>E N T and Obstetrics- Gynaec Cl</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/E-N-T-and-Obstetrics-Gynaec-Clinic-JEEVAN-SPECIALITY-CLINIC-Near-By-Retteri-Signal-And-Vinayagapuram-Bus-Stand-Kolathur/044PXX44-XX44-180829152802-R4F5_BZDET</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>08197200295</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>V S Hospital</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>http://www.vshospital.in</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/V-S-Hospital-Opposite-Road-Vijaya-Raja-Kalyana-Mandapam-Kovilambakkam/044PXX44-XX44-140327123600-Q7X1_BZDET</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>09740015984</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Narbhavi Cl</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Narbhavi-Clinic-Near-Indira-Gandhi-Statute-Perungalathur/044PXX44-XX44-170429114503-Y4L1_BZDET</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>07041604955</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Dr. Sanjeev - Pediatrician In Royapuram - Srk Child Care Cl</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Dr-Sanjeev-Pediatrician-In-Royapuram-Srk-Child-Care-Clinic-Vaccination-Center-Near-Dhanalakshmi-Higher-Secondary-School-Royapuram/044PXX44-XX44-250905025300-J5K5_BZDET</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>09035699430</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Recnac Oncology Cl</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>http://www.recnaconcology.com</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Recnac-Oncology-Clinic-Pondy-Bazaar-T-Nagar/044PXX44-XX44-170127202547-N8B6_BZDET</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>07405153244</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>K S Ortho Cl</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>http://www.ksorthochennai.com</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/K-S-Ortho-Clinic-Opposite-Amaravathi-Avenue-Park-Square-Colony-Puzhuthivakkam-Madipakkam/044PXX44-XX44-130224144339-B2J1_BZDET</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>09724862822</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Optilenz.com</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>http://www.optilenz.com</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Optilenzcom-Near-By-Vijay-House-Saligramam/044PXX44-XX44-220918104244-K7Z3_BZDET</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>08460409734</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Dr. Sundars Homeopathy</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Dr-Sundars-Homeopathy-Opp-Abirami-Mall-Kilpauk/044PXX44-XX44-101031220825-H9B4_BZDET</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>09035772470</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Lapser Cl</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>http://www.lapser.in</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Lapser-Clinic-Next-Cannon-Store-Room-Tansy-Nagar-Velacheri/044PXX44-XX44-230518063246-E6W2_BZDET</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>09035107035</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Sri Jayam Cl</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Sri-Jayam-Clinic-Opposite-To-Anna-Arch-Near-Skywalk-Aminjikarai/044PXX44-XX44-120403111553-F5C5_BZDET</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>07411657051</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Dr Vijay Balaji</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>http://www.hipkneetreatment.in</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Dr-Vijay-Balaji-Near-Ibaco-Ice-Cream-Gopalapuram/044PXX44-XX44-200203175215-F8K8_BZDET</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>08147718016</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>WHITE STONES PEDIATRIC THERAPY CENTRE</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/WHITE-STONES-PEDIATRIC-THERAPY-CENTRE-Near-Decor-Shop-Moolakadai-Kodungaiyur/044PXX44-XX44-250217091156-I5B9_BZDET</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>08904961252</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Shri Loganathan Family Cl</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Shri-Loganathan-Family-Clinic-Near-Post-Office-Saidapet/044PXX44-XX44-180108150845-X1Z7_BZDET</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>07383384538</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Ecr Multispeciality Cl</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>http://www.emchealth.in</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Ecr-Multispeciality-Clinic-EMC-Near-Palavakkam-Periyar-Salai-Signal-Palavakkam/044PXX44-XX44-220518123241-D6K5_BZDET</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>09731954719</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Ayush Piles &amp; Fistula Cl</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>http://www.ayushpilesfistula.com</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Ayush-Piles-Fistula-Clinic-Near-By-Nathamuni-Signal-Villivakkam/044PXX44-XX44-220506180542-Y7E7_BZDET</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>08147022048</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Hear</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>http://www.hearingcentre.co.in</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Hearing-Centre-Nungambakkam-Nungambakkam/044PXX44-XX44-121127114330-E3B9_BZDET</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>08197257391</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Murugan Hospitals</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>http://www.muruganhospitals.in</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Murugan-Hospitals-Kilpauk-Kilpauk/044PXX44-XX44-151217183033-A2W3_BZDET</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Dr. Palaniappan T</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>http://www.medwayhospitals.com</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Dr-Palaniappan-T-Kodambakkam-Kodambakkam/044PXX44-XX44-120821145819-J7M4_BZDET</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Medway Hospitals</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>http://www.medwayhospitals.com</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Medway-Hospitals-Kodambakkam-Kodambakkam/044PXX44-XX44-121029203819-D5I8_BZDET</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>08147151873</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Ramakrishnan Dental Cl</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Ramakrishnan-Dental-Clinic-Adambakkam/044PXX44-XX44-241202201532-S2W3_BZDET</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>09035107035</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Kottakkal Cl</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Kottakkal-Clinic-Location-Besant-Nagar/044PXX44-XX44-241202230956-C3M5_BZDET</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>08511444824</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Rahims Dental Cl</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Rahims-Dental-Clinic/044PXX44-XX44-241202201529-J6V4_BZDET</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>09724923504</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Star White Dental Cl</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Star-White-Dental-Clinic-Kamarajapuram/044PXX44-XX44-241202201649-H6B7_BZDET</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>09035216995</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Sivakumar Fitness Studio (Closed Down)</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Sivakumar-Fitness-Studio-Closed-Down-Anna-Nagar-West/044PXX44-XX44-210125122317-K3H1_BZDET</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Dark Knight Unisex Fitness Centre</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Dark-Knight-Unisex-Fitness-Centre-Near-Old-Mgr-Nagar-Police-Station-Jafferkhanpet/044PXX44-XX44-220131091416-Z6M9_BZDET</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>08105743154</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Slam Lifestyle And Fitness Studio</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>http://www.slamfitnessstudio.in</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Slam-Lifestyle-And-Fitness-Studio-Opp-To-Holiday-In-Thoraipakkam/044PXX44-XX44-200108115631-P9V3_BZDET</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>08197311674</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Reboot Fitness</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Reboot-Fitness-Above-Tanishq-Jewellery-Iyyappanthangal/044PXX44-XX44-230821125438-K2D2_BZDET</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>07048631968</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Levels Fitness Studio</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>https://www.levelsfitnessstudio.com</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Levels-Fitness-Studio-17E-Bus-Depo-Saligramam/044PXX44-XX44-240210001126-U5Q2_BZDET</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>08147937982</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Arrow Fitness Center</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Arrow-Fitness-Center-Near-Hindu-Vidyalaya-School-And-Opposite-Raju-Electricals-West-Mambalam/044PXX44-XX44-111231134424-Q5V7_BZDET</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>09740487068</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Hi Fi Foundation</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>http://www.hififoundation.org</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Hi-Fi-Foundation-Near-Theradi-Bus-Stop-Tiruvottiyur/044PXX44-XX44-240926175617-S7N8_BZDET</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>08485955714</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Burn Out Unisex Fitness Studio - Kottivakkam ECR</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>http://www.burnoutfitnessstudio.com/</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Burn-Out-Unisex-Fitness-Studio-Kottivakkam-ECR-Ecr-Main-Road-Kottivakkam/044PXX44-XX44-241016211225-J3Y5_BZDET</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>07041552692</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>S Fit Gym</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/S-Fit-Gym-Kilpauk/044PXX44-XX44-241202220123-S5Z7_BZDET</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>09740311082</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Mav Swimm</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Mav-Swimming-Pool-Near-Sembakkam-Bus-Stop-Sembakkam/044P5425037_BZDET</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>07947058632</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>S Fit Gym</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/S-Fit-Gym-Kilpauk/044PXX44-XX44-241202220123-S5Z7_BZDET</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>09740311082</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Slam Lifestyle and Fitness Studio</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Slam-Lifestyle-and-Fitness-Studio-Opposite-Rto-Office-Above-Poorvika-Mobile-Sholinganallur/044PXX44-XX44-181024223827-P7Y6_BZDET</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>07411668806</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Dark Knight Unisex Fitness Centre</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Dark-Knight-Unisex-Fitness-Centre-Near-Old-Mgr-Nagar-Police-Station-Jafferkhanpet/044PXX44-XX44-220131091416-Z6M9_BZDET</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>08105743154</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>F6 Unisex Gym</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/F6-Unisex-Gym-Near-By-Ellaiamman-Kovil-Mugalivakkam/044PXX44-XX44-240608083219-K4L9_BZDET</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>08401217591</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>O2 Health Studio</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>http://www.o2healthstudio.com</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/O2-Health-Studio-Opposite-Taj-Coromandel-Nungambakkam/044PF001290_BZDET</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>08401552844</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Mac Fitness Studio</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>http://www.macfitnessstudio.com</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Mac-Fitness-Studio-Near-Maharastra-Bank-Sri-Kapaleeshwarar-Nagar-Neelankarai/044PXX44-XX44-220604144540-F2F9_BZDET</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>07795691315</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>MOVDOC</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>http://www.functionalphysio.in</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/MOVDOC-Behind-Thalapakatti-Restaurant-Perungudi/044PXX44-XX44-201016152025-M2H8_BZDET</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>08460437769</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Levels Fitness Studio</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>https://www.levelsfitnessstudio.com</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Levels-Fitness-Studio-17E-Bus-Depo-Saligramam/044PXX44-XX44-240210001126-U5Q2_BZDET</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>08147937982</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Reboot Fitness</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Reboot-Fitness-Above-Tanishq-Jewellery-Iyyappanthangal/044PXX44-XX44-230821125438-K2D2_BZDET</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>07048631968</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Hi Fi Foundation</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>http://www.hififoundation.org</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Hi-Fi-Foundation-Near-Theradi-Bus-Stop-Tiruvottiyur/044PXX44-XX44-240926175617-S7N8_BZDET</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>08485955714</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Indian Power Gym</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>http://www.indianpowergym.com</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Indian-Power-Gym-Arumbakkam-Arumbakkam/044PF001328_BZDET</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Coach Deepak Ramesh</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>http://www.coachdeepak.com</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Coach-Deepak-Ramesh-Raja-Annamalai-Puram-Raja-Annamalai-Puram/044PXX44-XX44-210711232030-J8Q1_BZDET</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>09725746305</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>In And Out Fitness</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/In-And-Out-Fitness-George-Town-George-Town/044PXX44-XX44-161121130248-T5L5_BZDET</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Slam Lifestyle And Fitness Studio</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>http://www.paulsons.in/slam-fitness.php</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Slam-Lifestyle-And-Fitness-Studio-Perambur-Perambur/044PXX44-XX44-180528173556-E5F6_BZDET</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Mav Swimm</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Mav-Swimming-Pool-Near-Sembakkam-Bus-Stop-Sembakkam/044P5425037_BZDET</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>07947058632</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/justdial_leads.xlsx
+++ b/justdial_leads.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E197"/>
+  <dimension ref="A1:E212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5705,6 +5705,411 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Rjr Herbal Siddha Ayurveda Unani And Naturopathy Hospitals</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>http://www.rjrherbalhospitals.com</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Rjr-Herbal-Siddha-Ayurveda-Unani-And-Naturopathy-Hospitals-Opposite-Post-Office-T-Nagar/044PXX44-XX44-180622215408-D3H6_BZDET</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>07947066565</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Homeocare International Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>http://www.homeocare.in</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Homeocare-International-Pvt-Ltd-Besides-Aarthi-Scans-Tambaram-West/044PXX44-XX44-140515163104-S5H1_BZDET</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>09731979204</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Apollo Cl</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>http://www.apolloclinic.com/clinic-locator/india/tamil-nadu/chennai/porur</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Apollo-Clinic-Opp-Tanisq-Showroom-Opp-Prestige-Bella-Vista-Apts-Kattupakkam/044PXX44-XX44-230905160944-C6V5_BZDET</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>08460418794</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Dr Vijay Balaji</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>http://www.hipkneetreatment.in</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Dr-Vijay-Balaji-Near-Ibaco-Ice-Cream-Gopalapuram/044PXX44-XX44-200203175215-F8K8_BZDET</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>08147718016</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Dr. Kamakshi Multispeciality Cl</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>http://www.drkmh.com</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Dr-Kamakshi-Multispeciality-Clinic-Opposite-Yamaha-Showroom-Vgp-Pushpa-Nagar-Medavakkam/044PXX44-XX44-190905110259-V3R4_BZDET</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>08401068352</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Sanjeevi Pharma</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>http://www.sanjeevipharma.com</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Sanjeevi-Pharma-Opp-To-Anna-Siddha-Medical-College-Arumbakkam/044P7019021_BZDET</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>08147817803</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Thulir Multispeciality Cl</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Thulir-Multispeciality-Clinic-Near-To-Perumal-Koil-Kolathur/044PXX44-XX44-190424112157-S4X6_BZDET</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>08147726585</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Dr. Sanjeev - Pediatrician In Royapuram - Srk Child Care Cl</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Dr-Sanjeev-Pediatrician-In-Royapuram-Srk-Child-Care-Clinic-Vaccination-Center-Near-Dhanalakshmi-Higher-Secondary-School-Royapuram/044PXX44-XX44-250905025300-J5K5_BZDET</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>09035699430</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>K S Ortho Cl</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>http://www.ksorthochennai.com</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/K-S-Ortho-Clinic-Opposite-Amaravathi-Avenue-Park-Square-Colony-Puzhuthivakkam-Madipakkam/044PXX44-XX44-130224144339-B2J1_BZDET</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>09724862822</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Dr. Sundars Homeopathy</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>No Website</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Dr-Sundars-Homeopathy-Opp-Abirami-Mall-Kilpauk/044PXX44-XX44-101031220825-H9B4_BZDET</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>09035772470</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Vdm Health Facility</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>https://manickamthiru.com/</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Vdm-Health-Facility-Next-To-Sangam-Cinema-Hall-Kilpauk/044P9037456_BZDET</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>08460280112</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Hear</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>http://www.hearingcentre.co.in</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Hearing-Centre-Nungambakkam-Nungambakkam/044PXX44-XX44-121127114330-E3B9_BZDET</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>08197257391</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Murugan Hospitals</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>http://www.muruganhospitals.in</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Murugan-Hospitals-Kilpauk-Kilpauk/044PXX44-XX44-151217183033-A2W3_BZDET</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Dr. Palaniappan T</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>http://www.medwayhospitals.com</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Dr-Palaniappan-T-Kodambakkam-Kodambakkam/044PXX44-XX44-120821145819-J7M4_BZDET</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Medway Hospitals</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>http://www.medwayhospitals.com</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>https://www.justdial.com/Chennai/Medway-Hospitals-Kodambakkam-Kodambakkam/044PXX44-XX44-121029203819-D5I8_BZDET</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>08147151873</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
